--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="166">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -493,6 +493,10 @@
   </si>
   <si>
     <t>fr-lm-observation-vital-sign.bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-body-structure
+</t>
   </si>
   <si>
     <t>Site de l'observation</t>
@@ -3203,13 +3207,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3277,10 +3281,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3306,10 +3310,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3360,7 +3364,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -3377,10 +3381,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3406,10 +3410,10 @@
         <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3439,10 +3443,10 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -3460,7 +3464,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3477,10 +3481,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3503,13 +3507,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3560,7 +3564,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>fr-lm-observation-vital-sign.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
-    <t>Patient/subject information</t>
+    <t>Patient / Usager</t>
   </si>
   <si>
     <t>fr-lm-entry.header.subject</t>
@@ -443,7 +443,7 @@
     <t>fr-lm-entry.header.source</t>
   </si>
   <si>
-    <t>fr-lm-observation-vital-sign.header.langue</t>
+    <t>fr-lm-observation-vital-sign.header.language</t>
   </si>
   <si>
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
@@ -451,7 +451,7 @@
 La partie en majuscules indique le code pays (ISO-3166)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.langue</t>
+    <t>fr-lm-entry.header.language</t>
   </si>
   <si>
     <t>fr-lm-observation-vital-sign.observationDate[x]</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="161">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,13 +422,7 @@
 </t>
   </si>
   <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+    <t>Statut</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -474,16 +468,6 @@
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-signe-vital-cisis</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-vital-sign.status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Statut de l'entrée</t>
   </si>
   <si>
     <t>fr-lm-observation-vital-sign.method</t>
@@ -829,7 +813,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ27"/>
+  <dimension ref="A1:AJ26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="58.58984375" customWidth="true" bestFit="true"/>
@@ -2543,31 +2527,31 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF17" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="Z17" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF17" t="s" s="2">
-        <v>135</v>
-      </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2581,10 +2565,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2610,10 +2594,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2664,7 +2648,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2681,10 +2665,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2710,10 +2694,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2764,7 +2748,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2781,10 +2765,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2807,13 +2791,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2864,7 +2848,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2881,10 +2865,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2910,10 +2894,10 @@
         <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2943,10 +2927,10 @@
         <v>73</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>73</v>
@@ -2964,7 +2948,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -2981,10 +2965,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2992,7 +2976,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>79</v>
@@ -3007,13 +2991,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3064,10 +3048,10 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>79</v>
@@ -3081,10 +3065,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3107,13 +3091,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>131</v>
+        <v>150</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3164,7 +3148,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3181,10 +3165,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3192,7 +3176,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>79</v>
@@ -3207,13 +3191,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3264,10 +3248,10 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
         <v>79</v>
@@ -3281,10 +3265,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3292,10 +3276,10 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>73</v>
@@ -3310,10 +3294,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3343,10 +3327,10 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>73</v>
+        <v>156</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>73</v>
+        <v>157</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>73</v>
@@ -3364,13 +3348,13 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>73</v>
@@ -3381,10 +3365,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3395,7 +3379,7 @@
         <v>74</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>73</v>
@@ -3407,7 +3391,7 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>131</v>
+        <v>159</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>160</v>
@@ -3443,10 +3427,10 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>161</v>
+        <v>73</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>162</v>
+        <v>73</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -3464,118 +3448,18 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="C27" s="2"/>
-      <c r="D27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E27" s="2"/>
-      <c r="F27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K27" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q27" s="2"/>
-      <c r="R27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="AG27" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-observation-vital-sign.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
